--- a/sampleprojects/Cribbage/excel/Cribbage.xlsx
+++ b/sampleprojects/Cribbage/excel/Cribbage.xlsx
@@ -13,13 +13,18 @@
     <sheet name="Score Pairs" sheetId="5" r:id="rId8"/>
     <sheet name="Score Flush" sheetId="6" r:id="rId9"/>
     <sheet name="Score Nobs" sheetId="7" r:id="rId10"/>
+    <sheet name="Score Play" sheetId="8" r:id="rId11"/>
+    <sheet name="Score Play Count" sheetId="9" r:id="rId12"/>
+    <sheet name="Score Play Pairs" sheetId="10" r:id="rId13"/>
+    <sheet name="Score Play Runs" sheetId="11" r:id="rId14"/>
+    <sheet name="Score Play Go" sheetId="12" r:id="rId15"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>DT: Score Hand</t>
   </si>
@@ -265,6 +270,171 @@
   </si>
   <si>
     <t>His nobs for 1</t>
+  </si>
+  <si>
+    <t>DT: Score Play</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3060</t>
+  </si>
+  <si>
+    <t>set play.count_points = 0; set play.pair_points = 0; set play.run_points = 0; set play.go_points = 0; set play.total = 0;</t>
+  </si>
+  <si>
+    <t>suffixes(play.cards, 2, "rank", "combo", play.windows)</t>
+  </si>
+  <si>
+    <t>perform Score_Play_Count</t>
+  </si>
+  <si>
+    <t>perform Score_Play_Pairs</t>
+  </si>
+  <si>
+    <t>perform Score_Play_Runs</t>
+  </si>
+  <si>
+    <t>perform Score_Play_Go</t>
+  </si>
+  <si>
+    <t>set play.total = play.count_points + play.pair_points + play.run_points + play.go_points;</t>
+  </si>
+  <si>
+    <t>DT: Score Play Count</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3070</t>
+  </si>
+  <si>
+    <t>no card was laid on a go</t>
+  </si>
+  <si>
+    <t>play.is_go</t>
+  </si>
+  <si>
+    <t>fifteen</t>
+  </si>
+  <si>
+    <t>play.count == 15</t>
+  </si>
+  <si>
+    <t>thirty-one</t>
+  </si>
+  <si>
+    <t>play.count == 31</t>
+  </si>
+  <si>
+    <t>add 2 to play.count_points</t>
+  </si>
+  <si>
+    <t>Thirty-one for 2</t>
+  </si>
+  <si>
+    <t>DT: Score Play Pairs</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3080</t>
+  </si>
+  <si>
+    <t>for all play.windows</t>
+  </si>
+  <si>
+    <t>every card in the window shares a rank</t>
+  </si>
+  <si>
+    <t>combo.distinct == 1</t>
+  </si>
+  <si>
+    <t>only the longest trailing block counts</t>
+  </si>
+  <si>
+    <t>play.pair_points == 0</t>
+  </si>
+  <si>
+    <t>four of a kind</t>
+  </si>
+  <si>
+    <t>combo.count == 4</t>
+  </si>
+  <si>
+    <t>three of a kind</t>
+  </si>
+  <si>
+    <t>combo.count == 3</t>
+  </si>
+  <si>
+    <t>combo.count == 2</t>
+  </si>
+  <si>
+    <t>add 12 to play.pair_points</t>
+  </si>
+  <si>
+    <t>add 6 to play.pair_points</t>
+  </si>
+  <si>
+    <t>add 2 to play.pair_points</t>
+  </si>
+  <si>
+    <t>DT: Score Play Runs</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3090</t>
+  </si>
+  <si>
+    <t>only the longest run counts</t>
+  </si>
+  <si>
+    <t>play.run_points == 0</t>
+  </si>
+  <si>
+    <t>runs start at three</t>
+  </si>
+  <si>
+    <t>combo.count &gt;= 3</t>
+  </si>
+  <si>
+    <t>no rank repeats</t>
+  </si>
+  <si>
+    <t>combo.distinct == combo.count</t>
+  </si>
+  <si>
+    <t>ranks are consecutive in some order</t>
+  </si>
+  <si>
+    <t>combo.spread == combo.count - 1</t>
+  </si>
+  <si>
+    <t>set play.run_points = combo.count;</t>
+  </si>
+  <si>
+    <t>A run of {combo.count}</t>
+  </si>
+  <si>
+    <t>DT: Score Play Go</t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 3100</t>
+  </si>
+  <si>
+    <t>thirty-one supersedes the single point</t>
+  </si>
+  <si>
+    <t>last card of the whole play</t>
+  </si>
+  <si>
+    <t>play.is_last</t>
+  </si>
+  <si>
+    <t>opponent said go and this side cannot play either</t>
+  </si>
+  <si>
+    <t>add 1 to play.go_points</t>
+  </si>
+  <si>
+    <t>One for last card</t>
+  </si>
+  <si>
+    <t>One for the go</t>
   </si>
 </sst>
 </file>
@@ -624,6 +794,2436 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>3</v>
+      </c>
+      <c r="G18" s="4">
+        <v>4</v>
+      </c>
+      <c r="H18" s="4">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4">
+        <v>6</v>
+      </c>
+      <c r="J18" s="4">
+        <v>7</v>
+      </c>
+      <c r="K18" s="4">
+        <v>8</v>
+      </c>
+      <c r="L18" s="4">
+        <v>9</v>
+      </c>
+      <c r="M18" s="4">
+        <v>10</v>
+      </c>
+      <c r="N18" s="4">
+        <v>11</v>
+      </c>
+      <c r="O18" s="4">
+        <v>12</v>
+      </c>
+      <c r="P18" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>14</v>
+      </c>
+      <c r="R18" s="4">
+        <v>15</v>
+      </c>
+      <c r="S18" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5</v>
+      </c>
+      <c r="I23" s="1">
+        <v>6</v>
+      </c>
+      <c r="J23" s="1">
+        <v>7</v>
+      </c>
+      <c r="K23" s="1">
+        <v>8</v>
+      </c>
+      <c r="L23" s="1">
+        <v>9</v>
+      </c>
+      <c r="M23" s="1">
+        <v>10</v>
+      </c>
+      <c r="N23" s="1">
+        <v>11</v>
+      </c>
+      <c r="O23" s="1">
+        <v>12</v>
+      </c>
+      <c r="P23" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>14</v>
+      </c>
+      <c r="R23" s="1">
+        <v>15</v>
+      </c>
+      <c r="S23" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
+        <v>3</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A23:B23"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>3</v>
+      </c>
+      <c r="G17" s="4">
+        <v>4</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
+        <v>6</v>
+      </c>
+      <c r="J17" s="4">
+        <v>7</v>
+      </c>
+      <c r="K17" s="4">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4">
+        <v>9</v>
+      </c>
+      <c r="M17" s="4">
+        <v>10</v>
+      </c>
+      <c r="N17" s="4">
+        <v>11</v>
+      </c>
+      <c r="O17" s="4">
+        <v>12</v>
+      </c>
+      <c r="P17" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>14</v>
+      </c>
+      <c r="R17" s="4">
+        <v>15</v>
+      </c>
+      <c r="S17" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1">
+        <v>7</v>
+      </c>
+      <c r="K20" s="1">
+        <v>8</v>
+      </c>
+      <c r="L20" s="1">
+        <v>9</v>
+      </c>
+      <c r="M20" s="1">
+        <v>10</v>
+      </c>
+      <c r="N20" s="1">
+        <v>11</v>
+      </c>
+      <c r="O20" s="1">
+        <v>12</v>
+      </c>
+      <c r="P20" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>14</v>
+      </c>
+      <c r="R20" s="1">
+        <v>15</v>
+      </c>
+      <c r="S20" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>3</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
+        <v>9</v>
+      </c>
+      <c r="M18" s="1">
+        <v>10</v>
+      </c>
+      <c r="N18" s="1">
+        <v>11</v>
+      </c>
+      <c r="O18" s="1">
+        <v>12</v>
+      </c>
+      <c r="P18" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>14</v>
+      </c>
+      <c r="R18" s="1">
+        <v>15</v>
+      </c>
+      <c r="S18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -4825,4 +7425,1388 @@
     <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4</v>
+      </c>
+      <c r="H12" s="1">
+        <v>5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>6</v>
+      </c>
+      <c r="J12" s="1">
+        <v>7</v>
+      </c>
+      <c r="K12" s="1">
+        <v>8</v>
+      </c>
+      <c r="L12" s="1">
+        <v>9</v>
+      </c>
+      <c r="M12" s="1">
+        <v>10</v>
+      </c>
+      <c r="N12" s="1">
+        <v>11</v>
+      </c>
+      <c r="O12" s="1">
+        <v>12</v>
+      </c>
+      <c r="P12" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>14</v>
+      </c>
+      <c r="R12" s="1">
+        <v>15</v>
+      </c>
+      <c r="S12" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="C10:S10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>3</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
+      <c r="H15" s="4">
+        <v>5</v>
+      </c>
+      <c r="I15" s="4">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
+        <v>9</v>
+      </c>
+      <c r="M15" s="4">
+        <v>10</v>
+      </c>
+      <c r="N15" s="4">
+        <v>11</v>
+      </c>
+      <c r="O15" s="4">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>15</v>
+      </c>
+      <c r="S15" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
+        <v>9</v>
+      </c>
+      <c r="M18" s="1">
+        <v>10</v>
+      </c>
+      <c r="N18" s="1">
+        <v>11</v>
+      </c>
+      <c r="O18" s="1">
+        <v>12</v>
+      </c>
+      <c r="P18" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>14</v>
+      </c>
+      <c r="R18" s="1">
+        <v>15</v>
+      </c>
+      <c r="S18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/sampleprojects/Cribbage/excel/Cribbage.xlsx
+++ b/sampleprojects/Cribbage/excel/Cribbage.xlsx
@@ -53,7 +53,7 @@
     <t/>
   </si>
   <si>
-    <t>set hand.fifteen_points = 0; set hand.pair_points = 0; set hand.run_points = 0; set hand.flush_points = 0; set hand.nobs_points = 0; set hand.total = 0;</t>
+    <t>set hand.fifteen_points = 0; set hand.pair_points = 0; set hand.run_points = 0; set hand.flush_points = 0; set hand.nobs_points = 0; set hand.total = 0; for all hand.cards where card.rank &gt; 10 set card.value = 10; for all hand.cards where card.rank &lt;= 10 set card.value = card.rank; if number of hand.kept == 0 then for all hand.cards where card.is_starter == false add card to hand.kept; for all hand.cards where card.is_starter set hand.starter_suit = card.suit; endif;</t>
   </si>
   <si>
     <t>subsets(hand.cards, "combo", "value", hand.combos)</t>
